--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.82893241304273</v>
+        <v>6.472201517119443</v>
       </c>
       <c r="D2" t="n">
-        <v>2.161853628512133</v>
+        <v>0.3513012146332216</v>
       </c>
       <c r="E2" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F2" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.56827322466086</v>
+        <v>8.05484439900739</v>
       </c>
       <c r="D3" t="n">
-        <v>9.013878188659973</v>
+        <v>1.464755205657246</v>
       </c>
       <c r="E3" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F3" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.618185056084107</v>
+        <v>1.400455071613667</v>
       </c>
       <c r="D4" t="n">
-        <v>3.517543992706163</v>
+        <v>0.5716008988147515</v>
       </c>
       <c r="E4" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F4" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.09421200139941</v>
+        <v>1.802809450227405</v>
       </c>
       <c r="D5" t="n">
-        <v>10.42151127012544</v>
+        <v>1.693495581395384</v>
       </c>
       <c r="E5" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F5" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.89520617520792</v>
+        <v>5.670471003471288</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99709693447876</v>
+        <v>5.037028251852798</v>
       </c>
       <c r="E6" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F6" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.38928209054047</v>
+        <v>5.913258339712827</v>
       </c>
       <c r="D7" t="n">
-        <v>36.68097657490257</v>
+        <v>5.960658693421668</v>
       </c>
       <c r="E7" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F7" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.81011543556361</v>
+        <v>2.894143758279086</v>
       </c>
       <c r="D8" t="n">
-        <v>16.84051511142289</v>
+        <v>2.73658370560622</v>
       </c>
       <c r="E8" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F8" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.53019285806784</v>
+        <v>7.886156339436025</v>
       </c>
       <c r="D9" t="n">
-        <v>35.37417163632096</v>
+        <v>5.748302890902156</v>
       </c>
       <c r="E9" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F9" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.65413613616328</v>
+        <v>4.331297122126533</v>
       </c>
       <c r="D10" t="n">
-        <v>24.56741120695029</v>
+        <v>3.992204321129422</v>
       </c>
       <c r="E10" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F10" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.06864625629401</v>
+        <v>1.961155016647777</v>
       </c>
       <c r="D11" t="n">
-        <v>13.77318952813999</v>
+        <v>2.238143298322748</v>
       </c>
       <c r="E11" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F11" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>62.27827275819341</v>
+        <v>10.12021932320643</v>
       </c>
       <c r="D12" t="n">
-        <v>19.40255531027307</v>
+        <v>3.152915237919374</v>
       </c>
       <c r="E12" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F12" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.46166945440486</v>
+        <v>3.48752128634079</v>
       </c>
       <c r="D13" t="n">
-        <v>23.25673329231786</v>
+        <v>3.779219160001652</v>
       </c>
       <c r="E13" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F13" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.06269694171971</v>
+        <v>8.460188253029454</v>
       </c>
       <c r="D14" t="n">
-        <v>19.79409158290706</v>
+        <v>3.216539882222397</v>
       </c>
       <c r="E14" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F14" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.8966763692944</v>
+        <v>4.533209910010339</v>
       </c>
       <c r="D15" t="n">
-        <v>27.61316217134656</v>
+        <v>4.487138852843817</v>
       </c>
       <c r="E15" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F15" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.93834285553993</v>
+        <v>5.189980714025238</v>
       </c>
       <c r="D16" t="n">
-        <v>14.09170711843585</v>
+        <v>2.289902406745825</v>
       </c>
       <c r="E16" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F16" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.23127433834655</v>
+        <v>5.400082079981315</v>
       </c>
       <c r="D17" t="n">
-        <v>34.47263064737645</v>
+        <v>5.601802480198673</v>
       </c>
       <c r="E17" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F17" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>49.21136242880497</v>
+        <v>7.996846394680808</v>
       </c>
       <c r="D18" t="n">
-        <v>11.98692960228658</v>
+        <v>1.94787606037157</v>
       </c>
       <c r="E18" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F18" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.31054824265719</v>
+        <v>6.712964089431794</v>
       </c>
       <c r="D19" t="n">
-        <v>21.93394719143678</v>
+        <v>3.564266418608477</v>
       </c>
       <c r="E19" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F19" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.53122726830543</v>
+        <v>4.473824431099632</v>
       </c>
       <c r="D20" t="n">
-        <v>24.88473427625861</v>
+        <v>4.043769319892024</v>
       </c>
       <c r="E20" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F20" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>59.18415580973522</v>
+        <v>9.617425319081974</v>
       </c>
       <c r="D21" t="n">
-        <v>10.90998523270209</v>
+        <v>1.77287260031409</v>
       </c>
       <c r="E21" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F21" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>25.85281665218834</v>
+        <v>4.201082705980606</v>
       </c>
       <c r="D22" t="n">
-        <v>25.84181636297976</v>
+        <v>4.199295158984211</v>
       </c>
       <c r="E22" t="n">
-        <v>15.13733132771925</v>
+        <v>2.459816340754378</v>
       </c>
       <c r="F22" t="n">
-        <v>9.829724801821138</v>
+        <v>1.597330280295935</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
